--- a/data/trans_camb/P8_2_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P8_2_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 6,48</t>
+          <t>-2,73; 6,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 4,64</t>
+          <t>-4,43; 4,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 0,85</t>
+          <t>-7,07; 0,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,68; 1,44</t>
+          <t>-9,64; 1,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 1,55</t>
+          <t>-9,87; 1,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 0,67</t>
+          <t>-8,6; 0,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 2,82</t>
+          <t>-4,09; 2,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 1,63</t>
+          <t>-4,88; 2,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,22; -0,06</t>
+          <t>-6,04; 0,05</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-25,0; 68,45</t>
+          <t>-21,04; 70,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-29,36; 53,17</t>
+          <t>-32,86; 47,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-49,5; 10,8</t>
+          <t>-49,88; 8,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-50,07; 14,06</t>
+          <t>-51,48; 14,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-53,72; 14,29</t>
+          <t>-53,07; 10,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-45,83; 5,9</t>
+          <t>-45,35; 4,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-29,11; 24,47</t>
+          <t>-28,04; 24,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-36,16; 13,71</t>
+          <t>-32,42; 18,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-41,01; -0,37</t>
+          <t>-40,54; 0,4</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 6,48</t>
+          <t>-2,17; 7,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 6,42</t>
+          <t>-3,08; 6,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 6,74</t>
+          <t>-1,83; 6,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 7,83</t>
+          <t>-1,6; 7,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 9,29</t>
+          <t>-0,57; 9,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,3; 10,24</t>
+          <t>2,13; 10,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 5,93</t>
+          <t>-0,47; 5,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 6,1</t>
+          <t>0,16; 6,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,69; 7,39</t>
+          <t>1,57; 7,18</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-21,36; 98,59</t>
+          <t>-21,41; 113,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-20,66; 93,2</t>
+          <t>-27,4; 97,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-13,94; 102,98</t>
+          <t>-15,35; 113,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,06; 131,02</t>
+          <t>-16,44; 131,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 155,71</t>
+          <t>-6,73; 154,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,79; 177,9</t>
+          <t>19,31; 184,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 87,46</t>
+          <t>-5,21; 86,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 90,56</t>
+          <t>1,63; 89,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,56; 108,29</t>
+          <t>15,25; 104,91</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 9,8</t>
+          <t>1,39; 10,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 6,64</t>
+          <t>-1,65; 6,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,5; 69,67</t>
+          <t>2,83; 66,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 12,24</t>
+          <t>-6,08; 12,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 13,22</t>
+          <t>-7,16; 13,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 11,73</t>
+          <t>-5,05; 11,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 9,72</t>
+          <t>1,05; 9,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 6,78</t>
+          <t>-1,26; 6,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,43; 60,4</t>
+          <t>3,03; 59,45</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,09; 90,71</t>
+          <t>8,25; 90,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 62,01</t>
+          <t>-11,56; 63,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24,59; 607,95</t>
+          <t>21,56; 679,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-21,83; 66,74</t>
+          <t>-21,36; 67,08</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-25,2; 68,87</t>
+          <t>-24,6; 72,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-22,75; 59,14</t>
+          <t>-17,55; 64,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,83; 73,44</t>
+          <t>4,94; 67,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 50,24</t>
+          <t>-8,81; 49,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20,81; 447,64</t>
+          <t>18,73; 456,5</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 3,36</t>
+          <t>-3,4; 3,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 0,98</t>
+          <t>-5,49; 0,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 4,21</t>
+          <t>-2,97; 3,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 0,13</t>
+          <t>-7,97; -0,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,41; -0,81</t>
+          <t>-8,79; -0,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,52; -2,77</t>
+          <t>-14,79; -2,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 0,77</t>
+          <t>-4,2; 0,62</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,83; -1,01</t>
+          <t>-5,68; -0,88</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-8,0; -0,16</t>
+          <t>-8,62; -0,24</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-15,54; 18,86</t>
+          <t>-16,89; 19,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-24,98; 5,79</t>
+          <t>-26,76; 4,4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-12,23; 24,35</t>
+          <t>-14,34; 21,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-36,27; 0,66</t>
+          <t>-35,96; -0,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-37,82; -3,74</t>
+          <t>-39,59; -5,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-68,86; -14,65</t>
+          <t>-65,46; -13,23</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-21,66; 4,33</t>
+          <t>-20,85; 3,11</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-27,81; -5,17</t>
+          <t>-27,65; -4,89</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-39,87; -1,14</t>
+          <t>-43,62; -1,76</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 6,27</t>
+          <t>-4,01; 6,26</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 9,37</t>
+          <t>-1,23; 8,7</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 10,29</t>
+          <t>-0,71; 10,5</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,5; 17,39</t>
+          <t>7,36; 17,1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,99; 12,42</t>
+          <t>2,98; 12,71</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 11,19</t>
+          <t>-2,1; 11,67</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,01; 11,52</t>
+          <t>4,29; 11,58</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,1; 9,28</t>
+          <t>2,15; 9,3</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,02; 9,43</t>
+          <t>0,82; 9,62</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-22,06; 47,09</t>
+          <t>-21,31; 48,46</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 70,0</t>
+          <t>-6,96; 64,2</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 76,48</t>
+          <t>-4,02; 82,13</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>31,23; 95,62</t>
+          <t>31,6; 95,16</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>12,18; 68,39</t>
+          <t>12,74; 72,51</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 59,25</t>
+          <t>-7,48; 65,29</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,13; 66,89</t>
+          <t>19,85; 69,54</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>9,6; 53,8</t>
+          <t>9,88; 53,65</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>5,98; 54,52</t>
+          <t>4,19; 55,66</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 4,0</t>
+          <t>-2,22; 4,21</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 1,35</t>
+          <t>-3,79; 1,6</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 1,35</t>
+          <t>-3,99; 1,66</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 7,05</t>
+          <t>-0,85; 7,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 2,75</t>
+          <t>-5,35; 2,49</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 4,48</t>
+          <t>-3,25; 4,53</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 5,99</t>
+          <t>-1,14; 5,45</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 1,49</t>
+          <t>-5,18; 1,4</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 2,11</t>
+          <t>-4,67; 2,17</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-52,75; 194,44</t>
+          <t>-50,45; 244,3</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-80,97; 79,69</t>
+          <t>-80,42; 84,66</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-77,26; 81,22</t>
+          <t>-75,28; 105,97</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 22,67</t>
+          <t>-2,46; 23,32</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-15,14; 9,03</t>
+          <t>-15,63; 8,19</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 14,62</t>
+          <t>-9,38; 14,76</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 23,87</t>
+          <t>-4,05; 21,84</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-20,46; 5,67</t>
+          <t>-17,71; 5,06</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-16,01; 8,5</t>
+          <t>-16,17; 8,69</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 3,59</t>
+          <t>0,11; 3,47</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 2,31</t>
+          <t>-1,05; 2,25</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,8; 25,45</t>
+          <t>0,67; 24,07</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,52</t>
+          <t>0,34; 4,46</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 1,63</t>
+          <t>-2,57; 1,49</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 0,26</t>
+          <t>-5,55; 0,36</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,49</t>
+          <t>0,76; 3,53</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 1,36</t>
+          <t>-1,31; 1,29</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 13,44</t>
+          <t>-0,74; 12,94</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 27,68</t>
+          <t>0,64; 26,6</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 17,96</t>
+          <t>-7,2; 16,96</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>5,51; 188,94</t>
+          <t>4,66; 176,24</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2,25; 20,78</t>
+          <t>1,41; 20,0</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-10,53; 7,32</t>
+          <t>-10,53; 6,71</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-25,52; 1,1</t>
+          <t>-23,87; 1,3</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,45; 19,69</t>
+          <t>3,98; 19,85</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 7,6</t>
+          <t>-6,81; 7,22</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 73,98</t>
+          <t>-3,91; 70,92</t>
         </is>
       </c>
     </row>
